--- a/output/Princeton/TestEnvData.xlsx
+++ b/output/Princeton/TestEnvData.xlsx
@@ -824,16 +824,16 @@
         <v>08/13/2025</v>
       </c>
       <c r="C11" t="str">
-        <v>$14,030.00</v>
+        <v>$3,760.52</v>
       </c>
       <c r="D11" t="str">
-        <v>$14,030.00</v>
+        <v>$3,760.52</v>
       </c>
       <c r="E11" t="str">
-        <v>Humana</v>
+        <v>RFMS</v>
       </c>
       <c r="F11" t="str">
-        <v>HUMANA INC US LE EFTPAYMENT TRN**XXXXX*\</v>
+        <v>NDC CRT# DIRECT_DEP DIRECT_DEP</v>
       </c>
       <c r="G11" t="str">
         <v>Exact</v>
@@ -847,16 +847,16 @@
         <v>08/13/2025</v>
       </c>
       <c r="C12" t="str">
-        <v>$3,760.52</v>
+        <v>$14,030.00</v>
       </c>
       <c r="D12" t="str">
-        <v>$3,760.52</v>
+        <v>$14,030.00</v>
       </c>
       <c r="E12" t="str">
-        <v>RFMS</v>
+        <v>Humana</v>
       </c>
       <c r="F12" t="str">
-        <v>NDC CRT# DIRECT_DEP DIRECT_DEP</v>
+        <v>HUMANA INC US LE EFTPAYMENT TRN**XXXXX*\</v>
       </c>
       <c r="G12" t="str">
         <v>Exact</v>
@@ -1008,16 +1008,16 @@
         <v>08/20/2025</v>
       </c>
       <c r="C19" t="str">
-        <v>$6,285.00</v>
+        <v>$40.00</v>
       </c>
       <c r="D19" t="str">
-        <v>$6,285.00</v>
+        <v>$40.00</v>
       </c>
       <c r="E19" t="str">
-        <v>AARP</v>
+        <v>UHC</v>
       </c>
       <c r="F19" t="str">
-        <v>AARP Supplementa HCCLAIMPMT TRN****</v>
+        <v>UnitedHealthcare HCCLAIMPMT TRN**T**</v>
       </c>
       <c r="G19" t="str">
         <v>Exact</v>
@@ -1054,16 +1054,16 @@
         <v>08/20/2025</v>
       </c>
       <c r="C21" t="str">
-        <v>$40.00</v>
+        <v>$6,285.00</v>
       </c>
       <c r="D21" t="str">
-        <v>$40.00</v>
+        <v>$6,285.00</v>
       </c>
       <c r="E21" t="str">
-        <v>UHC</v>
+        <v>AARP</v>
       </c>
       <c r="F21" t="str">
-        <v>UnitedHealthcare HCCLAIMPMT TRN**T**</v>
+        <v>AARP Supplementa HCCLAIMPMT TRN****</v>
       </c>
       <c r="G21" t="str">
         <v>Exact</v>
@@ -1077,22 +1077,22 @@
         <v>08/21/2025</v>
       </c>
       <c r="C22" t="str">
-        <v>$18,039.77</v>
+        <v>$0.03</v>
       </c>
       <c r="D22" t="str">
-        <v>$18,039.77</v>
+        <v>$0.03</v>
       </c>
       <c r="E22" t="str">
-        <v>Deposit</v>
+        <v>ECHO ACH</v>
       </c>
       <c r="F22" t="str">
-        <v>-</v>
+        <v>HNB - ECHO ACH XFR ECHO Health Provider Portal Pi</v>
       </c>
       <c r="G22" t="str">
         <v>Exact</v>
       </c>
     </row>
-    <row r="23" xml:space="preserve">
+    <row r="23">
       <c r="A23" t="str">
         <v>08/21/2025</v>
       </c>
@@ -1100,280 +1100,280 @@
         <v>08/21/2025</v>
       </c>
       <c r="C23" t="str">
+        <v>$181.23</v>
+      </c>
+      <c r="D23" t="str">
+        <v>$181.23</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Anthem</v>
+      </c>
+      <c r="F23" t="str">
+        <v>ANTHEM BLUE KYC HCCLAIMPMT TRN***\</v>
+      </c>
+      <c r="G23" t="str">
+        <v>Exact</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>08/21/2025</v>
+      </c>
+      <c r="B24" t="str">
+        <v>08/21/2025</v>
+      </c>
+      <c r="C24" t="str">
+        <v>$349.00</v>
+      </c>
+      <c r="D24" t="str">
+        <v>$349.00</v>
+      </c>
+      <c r="E24" t="str">
+        <v>ACH</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Princeton Nursin Settlement Princeton Nursing And</v>
+      </c>
+      <c r="G24" t="str">
+        <v>Exact</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>08/21/2025</v>
+      </c>
+      <c r="B25" t="str">
+        <v>08/21/2025</v>
+      </c>
+      <c r="C25" t="str">
+        <v>$385.00</v>
+      </c>
+      <c r="D25" t="str">
+        <v>$385.00</v>
+      </c>
+      <c r="E25" t="str">
+        <v>CC</v>
+      </c>
+      <c r="F25" t="str">
+        <v>BANKCARD MTOT DEP PRINCETON NURSING &amp; RE</v>
+      </c>
+      <c r="G25" t="str">
+        <v>Exact</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>08/21/2025</v>
+      </c>
+      <c r="B26" t="str">
+        <v>08/21/2025</v>
+      </c>
+      <c r="C26" t="str">
+        <v>$540.00</v>
+      </c>
+      <c r="D26" t="str">
+        <v>$540.00</v>
+      </c>
+      <c r="E26" t="str">
+        <v>ACH</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Princeton Nursin Settlement Princeton Nursing And</v>
+      </c>
+      <c r="G26" t="str">
+        <v>Exact</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>08/21/2025</v>
+      </c>
+      <c r="B27" t="str">
+        <v>08/21/2025</v>
+      </c>
+      <c r="C27" t="str">
+        <v>$756.00</v>
+      </c>
+      <c r="D27" t="str">
+        <v>$756.00</v>
+      </c>
+      <c r="E27" t="str">
+        <v>ACH</v>
+      </c>
+      <c r="F27" t="str">
+        <v>Princeton Nursin Settlement Princeton Nursing And</v>
+      </c>
+      <c r="G27" t="str">
+        <v>Exact</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>08/21/2025</v>
+      </c>
+      <c r="B28" t="str">
+        <v>08/21/2025</v>
+      </c>
+      <c r="C28" t="str">
+        <v>$850.43</v>
+      </c>
+      <c r="D28" t="str">
+        <v>$850.43</v>
+      </c>
+      <c r="E28" t="str">
+        <v>AARP</v>
+      </c>
+      <c r="F28" t="str">
+        <v>AARP Supplementa HCCLAIMPMT TRN****</v>
+      </c>
+      <c r="G28" t="str">
+        <v>Exact</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>08/21/2025</v>
+      </c>
+      <c r="B29" t="str">
+        <v>08/21/2025</v>
+      </c>
+      <c r="C29" t="str">
+        <v>$967.00</v>
+      </c>
+      <c r="D29" t="str">
+        <v>$967.00</v>
+      </c>
+      <c r="E29" t="str">
+        <v>RFMS</v>
+      </c>
+      <c r="F29" t="str">
+        <v>NDC CRT#AC W#DDCC W#DDCC</v>
+      </c>
+      <c r="G29" t="str">
+        <v>Exact</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>08/21/2025</v>
+      </c>
+      <c r="B30" t="str">
+        <v>08/21/2025</v>
+      </c>
+      <c r="C30" t="str">
+        <v>$1,414.00</v>
+      </c>
+      <c r="D30" t="str">
+        <v>$1,414.00</v>
+      </c>
+      <c r="E30" t="str">
+        <v>ACH</v>
+      </c>
+      <c r="F30" t="str">
+        <v>Princeton Nursin Settlement Princeton Nursing And</v>
+      </c>
+      <c r="G30" t="str">
+        <v>Exact</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>08/21/2025</v>
+      </c>
+      <c r="B31" t="str">
+        <v>08/21/2025</v>
+      </c>
+      <c r="C31" t="str">
+        <v>$1,461.00</v>
+      </c>
+      <c r="D31" t="str">
+        <v>$1,461.00</v>
+      </c>
+      <c r="E31" t="str">
+        <v>ACH</v>
+      </c>
+      <c r="F31" t="str">
+        <v>Princeton Nursin Settlement Princeton Nursing And</v>
+      </c>
+      <c r="G31" t="str">
+        <v>Exact</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>08/21/2025</v>
+      </c>
+      <c r="B32" t="str">
+        <v>08/21/2025</v>
+      </c>
+      <c r="C32" t="str">
+        <v>$1,629.00</v>
+      </c>
+      <c r="D32" t="str">
+        <v>$1,629.00</v>
+      </c>
+      <c r="E32" t="str">
+        <v>ACH</v>
+      </c>
+      <c r="F32" t="str">
+        <v>Princeton Nursin Settlement Princeton Nursing And</v>
+      </c>
+      <c r="G32" t="str">
+        <v>Exact</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>08/21/2025</v>
+      </c>
+      <c r="B33" t="str">
+        <v>08/21/2025</v>
+      </c>
+      <c r="C33" t="str">
+        <v>$2,858.00</v>
+      </c>
+      <c r="D33" t="str">
+        <v>$2,858.00</v>
+      </c>
+      <c r="E33" t="str">
+        <v>ACH</v>
+      </c>
+      <c r="F33" t="str">
+        <v>Princeton Nursin Settlement Princeton Nursing And</v>
+      </c>
+      <c r="G33" t="str">
+        <v>Exact</v>
+      </c>
+    </row>
+    <row r="34" xml:space="preserve">
+      <c r="A34" t="str">
+        <v>08/21/2025</v>
+      </c>
+      <c r="B34" t="str">
+        <v>08/21/2025</v>
+      </c>
+      <c r="C34" t="str">
         <v>$5,679.00</v>
       </c>
-      <c r="D23" t="str">
+      <c r="D34" t="str">
         <v>$5,679.00</v>
       </c>
-      <c r="E23" t="str" xml:space="preserve">
+      <c r="E34" t="str" xml:space="preserve">
         <v xml:space="preserve">1: $1,319.00 (ACH | 8/21)
 2: $555.00 (ACH | 8/21)
 3: $1,426.00 (ACH | 8/21)
 4: $740.00 (ACH | 8/21)
 5: $1,639.00 (ACH | 8/21)</v>
       </c>
-      <c r="F23" t="str" xml:space="preserve">
+      <c r="F34" t="str" xml:space="preserve">
         <v xml:space="preserve">1: $2,186.00 (Princeton Nursin Settlement Princeton Nursing And | 8/21)
 2: $3,493.00 (Princeton Nursin Settlement Princeton Nursing And | 8/21)</v>
       </c>
-      <c r="G23" t="str">
+      <c r="G34" t="str">
         <v>Many-to-Many</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>08/21/2025</v>
-      </c>
-      <c r="B24" t="str">
-        <v>08/21/2025</v>
-      </c>
-      <c r="C24" t="str">
-        <v>$850.43</v>
-      </c>
-      <c r="D24" t="str">
-        <v>$850.43</v>
-      </c>
-      <c r="E24" t="str">
-        <v>AARP</v>
-      </c>
-      <c r="F24" t="str">
-        <v>AARP Supplementa HCCLAIMPMT TRN****</v>
-      </c>
-      <c r="G24" t="str">
-        <v>Exact</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>08/21/2025</v>
-      </c>
-      <c r="B25" t="str">
-        <v>08/21/2025</v>
-      </c>
-      <c r="C25" t="str">
-        <v>$181.23</v>
-      </c>
-      <c r="D25" t="str">
-        <v>$181.23</v>
-      </c>
-      <c r="E25" t="str">
-        <v>Anthem</v>
-      </c>
-      <c r="F25" t="str">
-        <v>ANTHEM BLUE KYC HCCLAIMPMT TRN***\</v>
-      </c>
-      <c r="G25" t="str">
-        <v>Exact</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>08/21/2025</v>
-      </c>
-      <c r="B26" t="str">
-        <v>08/21/2025</v>
-      </c>
-      <c r="C26" t="str">
-        <v>$385.00</v>
-      </c>
-      <c r="D26" t="str">
-        <v>$385.00</v>
-      </c>
-      <c r="E26" t="str">
-        <v>CC</v>
-      </c>
-      <c r="F26" t="str">
-        <v>BANKCARD MTOT DEP PRINCETON NURSING &amp; RE</v>
-      </c>
-      <c r="G26" t="str">
-        <v>Exact</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v>08/21/2025</v>
-      </c>
-      <c r="B27" t="str">
-        <v>08/21/2025</v>
-      </c>
-      <c r="C27" t="str">
-        <v>$0.03</v>
-      </c>
-      <c r="D27" t="str">
-        <v>$0.03</v>
-      </c>
-      <c r="E27" t="str">
-        <v>ECHO ACH</v>
-      </c>
-      <c r="F27" t="str">
-        <v>HNB - ECHO ACH XFR ECHO Health Provider Portal Pi</v>
-      </c>
-      <c r="G27" t="str">
-        <v>Exact</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>08/21/2025</v>
-      </c>
-      <c r="B28" t="str">
-        <v>08/21/2025</v>
-      </c>
-      <c r="C28" t="str">
-        <v>$148,721.72</v>
-      </c>
-      <c r="D28" t="str">
-        <v>$148,721.72</v>
-      </c>
-      <c r="E28" t="str">
-        <v>MCD</v>
-      </c>
-      <c r="F28" t="str">
-        <v>MEDICAID HCCLAIMPMT TRN**E*MA*</v>
-      </c>
-      <c r="G28" t="str">
-        <v>Exact</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <v>08/21/2025</v>
-      </c>
-      <c r="B29" t="str">
-        <v>08/21/2025</v>
-      </c>
-      <c r="C29" t="str">
-        <v>$967.00</v>
-      </c>
-      <c r="D29" t="str">
-        <v>$967.00</v>
-      </c>
-      <c r="E29" t="str">
-        <v>RFMS</v>
-      </c>
-      <c r="F29" t="str">
-        <v>NDC CRT#AC W#DDCC W#DDCC</v>
-      </c>
-      <c r="G29" t="str">
-        <v>Exact</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="str">
-        <v>08/21/2025</v>
-      </c>
-      <c r="B30" t="str">
-        <v>08/21/2025</v>
-      </c>
-      <c r="C30" t="str">
-        <v>$6,578.08</v>
-      </c>
-      <c r="D30" t="str">
-        <v>$6,578.08</v>
-      </c>
-      <c r="E30" t="str">
-        <v>ACH</v>
-      </c>
-      <c r="F30" t="str">
-        <v>Princeton Nursin Settlement Princeton Nursing And</v>
-      </c>
-      <c r="G30" t="str">
-        <v>Exact</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="str">
-        <v>08/21/2025</v>
-      </c>
-      <c r="B31" t="str">
-        <v>08/21/2025</v>
-      </c>
-      <c r="C31" t="str">
-        <v>$540.00</v>
-      </c>
-      <c r="D31" t="str">
-        <v>$540.00</v>
-      </c>
-      <c r="E31" t="str">
-        <v>ACH</v>
-      </c>
-      <c r="F31" t="str">
-        <v>Princeton Nursin Settlement Princeton Nursing And</v>
-      </c>
-      <c r="G31" t="str">
-        <v>Exact</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="str">
-        <v>08/21/2025</v>
-      </c>
-      <c r="B32" t="str">
-        <v>08/21/2025</v>
-      </c>
-      <c r="C32" t="str">
-        <v>$756.00</v>
-      </c>
-      <c r="D32" t="str">
-        <v>$756.00</v>
-      </c>
-      <c r="E32" t="str">
-        <v>ACH</v>
-      </c>
-      <c r="F32" t="str">
-        <v>Princeton Nursin Settlement Princeton Nursing And</v>
-      </c>
-      <c r="G32" t="str">
-        <v>Exact</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="str">
-        <v>08/21/2025</v>
-      </c>
-      <c r="B33" t="str">
-        <v>08/21/2025</v>
-      </c>
-      <c r="C33" t="str">
-        <v>$1,461.00</v>
-      </c>
-      <c r="D33" t="str">
-        <v>$1,461.00</v>
-      </c>
-      <c r="E33" t="str">
-        <v>ACH</v>
-      </c>
-      <c r="F33" t="str">
-        <v>Princeton Nursin Settlement Princeton Nursing And</v>
-      </c>
-      <c r="G33" t="str">
-        <v>Exact</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="str">
-        <v>08/21/2025</v>
-      </c>
-      <c r="B34" t="str">
-        <v>08/21/2025</v>
-      </c>
-      <c r="C34" t="str">
-        <v>$1,414.00</v>
-      </c>
-      <c r="D34" t="str">
-        <v>$1,414.00</v>
-      </c>
-      <c r="E34" t="str">
-        <v>ACH</v>
-      </c>
-      <c r="F34" t="str">
-        <v>Princeton Nursin Settlement Princeton Nursing And</v>
-      </c>
-      <c r="G34" t="str">
-        <v>Exact</v>
-      </c>
-    </row>
-    <row r="35">
+    <row r="35" xml:space="preserve">
       <c r="A35" t="str">
         <v>08/21/2025</v>
       </c>
@@ -1381,144 +1381,144 @@
         <v>08/21/2025</v>
       </c>
       <c r="C35" t="str">
-        <v>$349.00</v>
+        <v>$6,488.12</v>
       </c>
       <c r="D35" t="str">
-        <v>$349.00</v>
-      </c>
-      <c r="E35" t="str">
-        <v>ACH</v>
-      </c>
-      <c r="F35" t="str">
-        <v>Princeton Nursin Settlement Princeton Nursing And</v>
-      </c>
-      <c r="G35" t="str">
-        <v>Exact</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="str">
-        <v>08/21/2025</v>
-      </c>
-      <c r="B36" t="str">
-        <v>08/21/2025</v>
-      </c>
-      <c r="C36" t="str">
-        <v>$2,858.00</v>
-      </c>
-      <c r="D36" t="str">
-        <v>$2,858.00</v>
-      </c>
-      <c r="E36" t="str">
-        <v>ACH</v>
-      </c>
-      <c r="F36" t="str">
-        <v>Princeton Nursin Settlement Princeton Nursing And</v>
-      </c>
-      <c r="G36" t="str">
-        <v>Exact</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="str">
-        <v>08/21/2025</v>
-      </c>
-      <c r="B37" t="str">
-        <v>08/21/2025</v>
-      </c>
-      <c r="C37" t="str">
-        <v>$1,629.00</v>
-      </c>
-      <c r="D37" t="str">
-        <v>$1,629.00</v>
-      </c>
-      <c r="E37" t="str">
-        <v>ACH</v>
-      </c>
-      <c r="F37" t="str">
-        <v>Princeton Nursin Settlement Princeton Nursing And</v>
-      </c>
-      <c r="G37" t="str">
-        <v>Exact</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="str">
-        <v>08/21/2025</v>
-      </c>
-      <c r="B38" t="str">
-        <v>08/21/2025</v>
-      </c>
-      <c r="C38" t="str">
-        <v>$6,930.00</v>
-      </c>
-      <c r="D38" t="str">
-        <v>$6,930.00</v>
-      </c>
-      <c r="E38" t="str">
-        <v>ACH</v>
-      </c>
-      <c r="F38" t="str">
-        <v>Princeton Nursin Settlement Princeton Nursing And</v>
-      </c>
-      <c r="G38" t="str">
-        <v>Exact</v>
-      </c>
-    </row>
-    <row r="39" xml:space="preserve">
-      <c r="A39" t="str">
-        <v>08/21/2025</v>
-      </c>
-      <c r="B39" t="str">
-        <v>08/21/2025</v>
-      </c>
-      <c r="C39" t="str">
         <v>$6,488.12</v>
       </c>
-      <c r="D39" t="str">
-        <v>$6,488.12</v>
-      </c>
-      <c r="E39" t="str" xml:space="preserve">
+      <c r="E35" t="str" xml:space="preserve">
         <v xml:space="preserve">1: $963.00 (ACH | 8/21)
 2: $1,403.00 (ACH | 8/21)
 3: $800.00 (ACH | 8/21)
 4: $2,656.00 (ACH | 8/21)
 5: $666.12 (ACH | 8/21)</v>
       </c>
-      <c r="F39" t="str">
+      <c r="F35" t="str">
         <v>Princeton Nursin Settlement Princeton Nursing And</v>
       </c>
-      <c r="G39" t="str">
+      <c r="G35" t="str">
         <v>Many-to-One</v>
       </c>
     </row>
-    <row r="40" xml:space="preserve">
-      <c r="A40" t="str">
-        <v>08/21/2025</v>
-      </c>
-      <c r="B40" t="str">
-        <v>08/21/2025</v>
-      </c>
-      <c r="C40" t="str">
+    <row r="36">
+      <c r="A36" t="str">
+        <v>08/21/2025</v>
+      </c>
+      <c r="B36" t="str">
+        <v>08/21/2025</v>
+      </c>
+      <c r="C36" t="str">
+        <v>$6,578.08</v>
+      </c>
+      <c r="D36" t="str">
+        <v>$6,578.08</v>
+      </c>
+      <c r="E36" t="str">
+        <v>ACH</v>
+      </c>
+      <c r="F36" t="str">
+        <v>Princeton Nursin Settlement Princeton Nursing And</v>
+      </c>
+      <c r="G36" t="str">
+        <v>Exact</v>
+      </c>
+    </row>
+    <row r="37" xml:space="preserve">
+      <c r="A37" t="str">
+        <v>08/21/2025</v>
+      </c>
+      <c r="B37" t="str">
+        <v>08/21/2025</v>
+      </c>
+      <c r="C37" t="str">
         <v>$6,836.00</v>
       </c>
-      <c r="D40" t="str">
+      <c r="D37" t="str">
         <v>$6,836.00</v>
       </c>
-      <c r="E40" t="str" xml:space="preserve">
+      <c r="E37" t="str" xml:space="preserve">
         <v xml:space="preserve">1: $1,103.00 (ACH | 8/21)
 2: $1,999.00 (ACH | 8/21)
 3: $2,016.00 (ACH | 8/21)
 4: $1,718.00 (ACH | 8/21)</v>
       </c>
+      <c r="F37" t="str">
+        <v>Princeton Nursin Settlement Princeton Nursing And</v>
+      </c>
+      <c r="G37" t="str">
+        <v>Many-to-One</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>08/21/2025</v>
+      </c>
+      <c r="B38" t="str">
+        <v>08/21/2025</v>
+      </c>
+      <c r="C38" t="str">
+        <v>$6,930.00</v>
+      </c>
+      <c r="D38" t="str">
+        <v>$6,930.00</v>
+      </c>
+      <c r="E38" t="str">
+        <v>ACH</v>
+      </c>
+      <c r="F38" t="str">
+        <v>Princeton Nursin Settlement Princeton Nursing And</v>
+      </c>
+      <c r="G38" t="str">
+        <v>Exact</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>08/21/2025</v>
+      </c>
+      <c r="B39" t="str">
+        <v>08/21/2025</v>
+      </c>
+      <c r="C39" t="str">
+        <v>$18,039.77</v>
+      </c>
+      <c r="D39" t="str">
+        <v>$18,039.77</v>
+      </c>
+      <c r="E39" t="str">
+        <v>Deposit</v>
+      </c>
+      <c r="F39" t="str">
+        <v>-</v>
+      </c>
+      <c r="G39" t="str">
+        <v>Exact</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>08/21/2025</v>
+      </c>
+      <c r="B40" t="str">
+        <v>08/21/2025</v>
+      </c>
+      <c r="C40" t="str">
+        <v>$148,721.72</v>
+      </c>
+      <c r="D40" t="str">
+        <v>$148,721.72</v>
+      </c>
+      <c r="E40" t="str">
+        <v>MCD</v>
+      </c>
       <c r="F40" t="str">
-        <v>Princeton Nursin Settlement Princeton Nursing And</v>
+        <v>MEDICAID HCCLAIMPMT TRN**E*MA*</v>
       </c>
       <c r="G40" t="str">
-        <v>Many-to-One</v>
-      </c>
-    </row>
-    <row r="41">
+        <v>Exact</v>
+      </c>
+    </row>
+    <row r="41" xml:space="preserve">
       <c r="A41" t="str">
         <v>08/22/2025</v>
       </c>
@@ -1526,22 +1526,23 @@
         <v>08/22/2025</v>
       </c>
       <c r="C41" t="str">
-        <v>$22,964.00</v>
+        <v>$3,328.48</v>
       </c>
       <c r="D41" t="str">
-        <v>$22,964.00</v>
-      </c>
-      <c r="E41" t="str">
-        <v>MCR</v>
+        <v>$3,328.48</v>
+      </c>
+      <c r="E41" t="str" xml:space="preserve">
+        <v xml:space="preserve">1: $2,533.48 (ACH | 8/22)
+2: $795.00 (ACH | 8/22)</v>
       </c>
       <c r="F41" t="str">
-        <v>J AB MAC KY - HCCLAIMPMT TRN**EFT**</v>
+        <v>Princeton Nursin Settlement Princeton Nursing And</v>
       </c>
       <c r="G41" t="str">
-        <v>Exact</v>
-      </c>
-    </row>
-    <row r="42" xml:space="preserve">
+        <v>Many-to-One</v>
+      </c>
+    </row>
+    <row r="42">
       <c r="A42" t="str">
         <v>08/22/2025</v>
       </c>
@@ -1549,20 +1550,19 @@
         <v>08/22/2025</v>
       </c>
       <c r="C42" t="str">
-        <v>$3,328.48</v>
+        <v>$22,964.00</v>
       </c>
       <c r="D42" t="str">
-        <v>$3,328.48</v>
-      </c>
-      <c r="E42" t="str" xml:space="preserve">
-        <v xml:space="preserve">1: $2,533.48 (ACH | 8/22)
-2: $795.00 (ACH | 8/22)</v>
+        <v>$22,964.00</v>
+      </c>
+      <c r="E42" t="str">
+        <v>MCR</v>
       </c>
       <c r="F42" t="str">
-        <v>Princeton Nursin Settlement Princeton Nursing And</v>
+        <v>J AB MAC KY - HCCLAIMPMT TRN**EFT**</v>
       </c>
       <c r="G42" t="str">
-        <v>Many-to-One</v>
+        <v>Exact</v>
       </c>
     </row>
     <row r="43">
@@ -1573,16 +1573,16 @@
         <v>08/25/2025</v>
       </c>
       <c r="C43" t="str">
-        <v>$5,750.07</v>
+        <v>$1,061.00</v>
       </c>
       <c r="D43" t="str">
-        <v>$5,750.07</v>
+        <v>$1,061.00</v>
       </c>
       <c r="E43" t="str">
-        <v>Aetna</v>
+        <v>ACH</v>
       </c>
       <c r="F43" t="str">
-        <v>AETNA AS HCCLAIMPMT TRN***</v>
+        <v>Princeton Nursin Settlement Princeton Nursing And</v>
       </c>
       <c r="G43" t="str">
         <v>Exact</v>
@@ -1596,16 +1596,16 @@
         <v>08/25/2025</v>
       </c>
       <c r="C44" t="str">
-        <v>$130,247.58</v>
+        <v>$5,750.07</v>
       </c>
       <c r="D44" t="str">
-        <v>$130,247.58</v>
+        <v>$5,750.07</v>
       </c>
       <c r="E44" t="str">
-        <v>MCR</v>
+        <v>Aetna</v>
       </c>
       <c r="F44" t="str">
-        <v>J AB MAC KY - HCCLAIMPMT TRN**EFT**</v>
+        <v>AETNA AS HCCLAIMPMT TRN***</v>
       </c>
       <c r="G44" t="str">
         <v>Exact</v>
@@ -1619,16 +1619,16 @@
         <v>08/25/2025</v>
       </c>
       <c r="C45" t="str">
-        <v>$1,061.00</v>
+        <v>$130,247.58</v>
       </c>
       <c r="D45" t="str">
-        <v>$1,061.00</v>
+        <v>$130,247.58</v>
       </c>
       <c r="E45" t="str">
-        <v>ACH</v>
+        <v>MCR</v>
       </c>
       <c r="F45" t="str">
-        <v>Princeton Nursin Settlement Princeton Nursing And</v>
+        <v>J AB MAC KY - HCCLAIMPMT TRN**EFT**</v>
       </c>
       <c r="G45" t="str">
         <v>Exact</v>
@@ -1665,16 +1665,16 @@
         <v>08/26/2025</v>
       </c>
       <c r="C47" t="str">
-        <v>$8,260.00</v>
+        <v>$2,071.00</v>
       </c>
       <c r="D47" t="str">
-        <v>$8,260.00</v>
+        <v>$2,071.00</v>
       </c>
       <c r="E47" t="str">
-        <v>Humana</v>
+        <v>ACH</v>
       </c>
       <c r="F47" t="str">
-        <v>HUMANA INS CO HCCLAIMPMT TRN***</v>
+        <v>Princeton Nursin Settlement Princeton Nursing And</v>
       </c>
       <c r="G47" t="str">
         <v>Exact</v>
@@ -1688,16 +1688,16 @@
         <v>08/26/2025</v>
       </c>
       <c r="C48" t="str">
-        <v>$2,071.00</v>
+        <v>$5,866.00</v>
       </c>
       <c r="D48" t="str">
-        <v>$2,071.00</v>
+        <v>$5,866.00</v>
       </c>
       <c r="E48" t="str">
-        <v>ACH</v>
+        <v>Tricare</v>
       </c>
       <c r="F48" t="str">
-        <v>Princeton Nursin Settlement Princeton Nursing And</v>
+        <v>WPS-TMEP CONTRAC HCCLAIMPMT TRN****WP</v>
       </c>
       <c r="G48" t="str">
         <v>Exact</v>
@@ -1711,16 +1711,16 @@
         <v>08/26/2025</v>
       </c>
       <c r="C49" t="str">
-        <v>$5,866.00</v>
+        <v>$8,260.00</v>
       </c>
       <c r="D49" t="str">
-        <v>$5,866.00</v>
+        <v>$8,260.00</v>
       </c>
       <c r="E49" t="str">
-        <v>Tricare</v>
+        <v>Humana</v>
       </c>
       <c r="F49" t="str">
-        <v>WPS-TMEP CONTRAC HCCLAIMPMT TRN****WP</v>
+        <v>HUMANA INS CO HCCLAIMPMT TRN***</v>
       </c>
       <c r="G49" t="str">
         <v>Exact</v>
@@ -1772,7 +1772,7 @@
         <v>Exact</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" xml:space="preserve">
       <c r="A52" t="str">
         <v>08/28/2025</v>
       </c>
@@ -1780,22 +1780,23 @@
         <v>08/28/2025</v>
       </c>
       <c r="C52" t="str">
-        <v>$129,748.14</v>
+        <v>$8,220.25</v>
       </c>
       <c r="D52" t="str">
-        <v>$129,748.14</v>
-      </c>
-      <c r="E52" t="str">
-        <v>MCD</v>
+        <v>$8,220.25</v>
+      </c>
+      <c r="E52" t="str" xml:space="preserve">
+        <v xml:space="preserve">1: $1,623.00 (ACH | 8/28)
+2: $6,597.25 (ACH | 8/28)</v>
       </c>
       <c r="F52" t="str">
-        <v>MEDICAID HCCLAIMPMT TRN**E*MA*</v>
+        <v>Princeton Nursin Settlement Princeton Nursing And</v>
       </c>
       <c r="G52" t="str">
-        <v>Exact</v>
-      </c>
-    </row>
-    <row r="53" xml:space="preserve">
+        <v>Many-to-One</v>
+      </c>
+    </row>
+    <row r="53">
       <c r="A53" t="str">
         <v>08/28/2025</v>
       </c>
@@ -1803,20 +1804,19 @@
         <v>08/28/2025</v>
       </c>
       <c r="C53" t="str">
-        <v>$8,220.25</v>
+        <v>$129,748.14</v>
       </c>
       <c r="D53" t="str">
-        <v>$8,220.25</v>
-      </c>
-      <c r="E53" t="str" xml:space="preserve">
-        <v xml:space="preserve">1: $1,623.00 (ACH | 8/28)
-2: $6,597.25 (ACH | 8/28)</v>
+        <v>$129,748.14</v>
+      </c>
+      <c r="E53" t="str">
+        <v>MCD</v>
       </c>
       <c r="F53" t="str">
-        <v>Princeton Nursin Settlement Princeton Nursing And</v>
+        <v>MEDICAID HCCLAIMPMT TRN**E*MA*</v>
       </c>
       <c r="G53" t="str">
-        <v>Many-to-One</v>
+        <v>Exact</v>
       </c>
     </row>
     <row r="54">
@@ -1827,16 +1827,16 @@
         <v>08/29/2025</v>
       </c>
       <c r="C54" t="str">
-        <v>$1,179.59</v>
+        <v>$1,028.00</v>
       </c>
       <c r="D54" t="str">
-        <v>$1,179.59</v>
+        <v>$1,028.00</v>
       </c>
       <c r="E54" t="str">
-        <v>Humana</v>
+        <v>ACH</v>
       </c>
       <c r="F54" t="str">
-        <v>HUMANA AHP HCCLAIMPMT TRN***</v>
+        <v>Princeton Nursin Settlement Princeton Nursing And</v>
       </c>
       <c r="G54" t="str">
         <v>Exact</v>
@@ -1850,16 +1850,16 @@
         <v>08/29/2025</v>
       </c>
       <c r="C55" t="str">
-        <v>$1,028.00</v>
+        <v>$1,179.59</v>
       </c>
       <c r="D55" t="str">
-        <v>$1,028.00</v>
+        <v>$1,179.59</v>
       </c>
       <c r="E55" t="str">
-        <v>ACH</v>
+        <v>Humana</v>
       </c>
       <c r="F55" t="str">
-        <v>Princeton Nursin Settlement Princeton Nursing And</v>
+        <v>HUMANA AHP HCCLAIMPMT TRN***</v>
       </c>
       <c r="G55" t="str">
         <v>Exact</v>
@@ -1895,7 +1895,7 @@
         <v>08/21/2025</v>
       </c>
       <c r="B2" t="str">
-        <v>$1,170.00</v>
+        <v>$59.49</v>
       </c>
       <c r="C2" t="str">
         <v>ACH</v>
@@ -1909,7 +1909,7 @@
         <v>08/21/2025</v>
       </c>
       <c r="B3" t="str">
-        <v>$583.00</v>
+        <v>$215.00</v>
       </c>
       <c r="C3" t="str">
         <v>ACH</v>
@@ -1923,7 +1923,7 @@
         <v>08/21/2025</v>
       </c>
       <c r="B4" t="str">
-        <v>$500.00</v>
+        <v>$276.06</v>
       </c>
       <c r="C4" t="str">
         <v>ACH</v>
@@ -1937,7 +1937,7 @@
         <v>08/21/2025</v>
       </c>
       <c r="B5" t="str">
-        <v>$1,494.00</v>
+        <v>$500.00</v>
       </c>
       <c r="C5" t="str">
         <v>ACH</v>
@@ -1951,7 +1951,7 @@
         <v>08/21/2025</v>
       </c>
       <c r="B6" t="str">
-        <v>$17,902.50</v>
+        <v>$583.00</v>
       </c>
       <c r="C6" t="str">
         <v>ACH</v>
@@ -1965,7 +1965,7 @@
         <v>08/21/2025</v>
       </c>
       <c r="B7" t="str">
-        <v>$215.00</v>
+        <v>$663.00</v>
       </c>
       <c r="C7" t="str">
         <v>ACH</v>
@@ -1979,7 +1979,7 @@
         <v>08/21/2025</v>
       </c>
       <c r="B8" t="str">
-        <v>$9,820.36</v>
+        <v>$1,159.00</v>
       </c>
       <c r="C8" t="str">
         <v>ACH</v>
@@ -1993,7 +1993,7 @@
         <v>08/21/2025</v>
       </c>
       <c r="B9" t="str">
-        <v>$8,951.25</v>
+        <v>$1,170.00</v>
       </c>
       <c r="C9" t="str">
         <v>ACH</v>
@@ -2007,7 +2007,7 @@
         <v>08/21/2025</v>
       </c>
       <c r="B10" t="str">
-        <v>$4,400.00</v>
+        <v>$1,186.00</v>
       </c>
       <c r="C10" t="str">
         <v>ACH</v>
@@ -2021,7 +2021,7 @@
         <v>08/21/2025</v>
       </c>
       <c r="B11" t="str">
-        <v>$8,951.25</v>
+        <v>$1,494.00</v>
       </c>
       <c r="C11" t="str">
         <v>ACH</v>
@@ -2035,7 +2035,7 @@
         <v>08/21/2025</v>
       </c>
       <c r="B12" t="str">
-        <v>$8,951.25</v>
+        <v>$2,537.94</v>
       </c>
       <c r="C12" t="str">
         <v>ACH</v>
@@ -2049,7 +2049,7 @@
         <v>08/21/2025</v>
       </c>
       <c r="B13" t="str">
-        <v>$59.49</v>
+        <v>$4,400.00</v>
       </c>
       <c r="C13" t="str">
         <v>ACH</v>
@@ -2063,7 +2063,7 @@
         <v>08/21/2025</v>
       </c>
       <c r="B14" t="str">
-        <v>$2,537.94</v>
+        <v>$8,951.25</v>
       </c>
       <c r="C14" t="str">
         <v>ACH</v>
@@ -2077,7 +2077,7 @@
         <v>08/21/2025</v>
       </c>
       <c r="B15" t="str">
-        <v>$276.06</v>
+        <v>$8,951.25</v>
       </c>
       <c r="C15" t="str">
         <v>ACH</v>
@@ -2091,7 +2091,7 @@
         <v>08/21/2025</v>
       </c>
       <c r="B16" t="str">
-        <v>$1,186.00</v>
+        <v>$8,951.25</v>
       </c>
       <c r="C16" t="str">
         <v>ACH</v>
@@ -2105,7 +2105,7 @@
         <v>08/21/2025</v>
       </c>
       <c r="B17" t="str">
-        <v>$663.00</v>
+        <v>$9,820.36</v>
       </c>
       <c r="C17" t="str">
         <v>ACH</v>
@@ -2119,7 +2119,7 @@
         <v>08/21/2025</v>
       </c>
       <c r="B18" t="str">
-        <v>$1,159.00</v>
+        <v>$17,902.50</v>
       </c>
       <c r="C18" t="str">
         <v>ACH</v>
@@ -2214,7 +2214,7 @@
         <v>08/27/2025</v>
       </c>
       <c r="B6" t="str">
-        <v>$1,862.11</v>
+        <v>$286.58</v>
       </c>
       <c r="C6" t="str">
         <v>NVOICEPAY VENDOR PMT APEX GLOBAL ERP CHANGE AN</v>
@@ -2242,7 +2242,7 @@
         <v>08/27/2025</v>
       </c>
       <c r="B8" t="str">
-        <v>$286.58</v>
+        <v>$1,862.11</v>
       </c>
       <c r="C8" t="str">
         <v>NVOICEPAY VENDOR PMT APEX GLOBAL ERP CHANGE AN</v>
@@ -2332,13 +2332,13 @@
         <v>08/04/2025</v>
       </c>
       <c r="B4" t="str">
-        <v>$3,789,000.00</v>
+        <v>$12,200.99</v>
       </c>
       <c r="C4" t="str">
-        <v>195 Incoming Money Transfer</v>
+        <v>275 ZBA Credit</v>
       </c>
       <c r="D4" t="str">
-        <v>INCOMING WIREMAMCC I LLCNOTPROVIDED</v>
+        <v>SWEEP FROM DDA</v>
       </c>
       <c r="E4" t="str">
         <v>-</v>
@@ -2349,13 +2349,13 @@
         <v>08/04/2025</v>
       </c>
       <c r="B5" t="str">
-        <v>$12,200.99</v>
+        <v>$3,789,000.00</v>
       </c>
       <c r="C5" t="str">
-        <v>275 ZBA Credit</v>
+        <v>195 Incoming Money Transfer</v>
       </c>
       <c r="D5" t="str">
-        <v>SWEEP FROM DDA</v>
+        <v>INCOMING WIREMAMCC I LLCNOTPROVIDED</v>
       </c>
       <c r="E5" t="str">
         <v>-</v>
@@ -2366,13 +2366,13 @@
         <v>08/05/2025</v>
       </c>
       <c r="B6" t="str">
-        <v>$12,563.03</v>
+        <v>$828.48</v>
       </c>
       <c r="C6" t="str">
         <v>275 ZBA Credit</v>
       </c>
       <c r="D6" t="str">
-        <v>SWEEP FROM DDA</v>
+        <v>FUND FROM DDA</v>
       </c>
       <c r="E6" t="str">
         <v>-</v>
@@ -2383,13 +2383,13 @@
         <v>08/05/2025</v>
       </c>
       <c r="B7" t="str">
-        <v>$828.48</v>
+        <v>$12,563.03</v>
       </c>
       <c r="C7" t="str">
         <v>275 ZBA Credit</v>
       </c>
       <c r="D7" t="str">
-        <v>FUND FROM DDA</v>
+        <v>SWEEP FROM DDA</v>
       </c>
       <c r="E7" t="str">
         <v>-</v>
@@ -2468,7 +2468,7 @@
         <v>08/13/2025</v>
       </c>
       <c r="B12" t="str">
-        <v>$9,983.38</v>
+        <v>$5,986.69</v>
       </c>
       <c r="C12" t="str">
         <v>275 ZBA Credit</v>
@@ -2485,7 +2485,7 @@
         <v>08/13/2025</v>
       </c>
       <c r="B13" t="str">
-        <v>$5,986.69</v>
+        <v>$9,983.38</v>
       </c>
       <c r="C13" t="str">
         <v>275 ZBA Credit</v>
@@ -2553,13 +2553,13 @@
         <v>08/18/2025</v>
       </c>
       <c r="B17" t="str">
-        <v>$3,435.00</v>
+        <v>$1,023.20</v>
       </c>
       <c r="C17" t="str">
         <v>275 ZBA Credit</v>
       </c>
       <c r="D17" t="str">
-        <v>SWEEP FROM DDA</v>
+        <v>FUND FROM DDA</v>
       </c>
       <c r="E17" t="str">
         <v>-</v>
@@ -2570,13 +2570,13 @@
         <v>08/18/2025</v>
       </c>
       <c r="B18" t="str">
-        <v>$3,464,000.00</v>
+        <v>$3,435.00</v>
       </c>
       <c r="C18" t="str">
-        <v>195 Incoming Money Transfer</v>
+        <v>275 ZBA Credit</v>
       </c>
       <c r="D18" t="str">
-        <v>INCOMING WIREMAMCC I LLCLOAN ADVANCE</v>
+        <v>SWEEP FROM DDA</v>
       </c>
       <c r="E18" t="str">
         <v>-</v>
@@ -2604,13 +2604,13 @@
         <v>08/18/2025</v>
       </c>
       <c r="B20" t="str">
-        <v>$1,023.20</v>
+        <v>$3,464,000.00</v>
       </c>
       <c r="C20" t="str">
-        <v>275 ZBA Credit</v>
+        <v>195 Incoming Money Transfer</v>
       </c>
       <c r="D20" t="str">
-        <v>FUND FROM DDA</v>
+        <v>INCOMING WIREMAMCC I LLCLOAN ADVANCE</v>
       </c>
       <c r="E20" t="str">
         <v>-</v>
@@ -2621,13 +2621,13 @@
         <v>08/19/2025</v>
       </c>
       <c r="B21" t="str">
-        <v>$8,421.72</v>
+        <v>$992.76</v>
       </c>
       <c r="C21" t="str">
         <v>275 ZBA Credit</v>
       </c>
       <c r="D21" t="str">
-        <v>SWEEP FROM DDA</v>
+        <v>FUND FROM DDA</v>
       </c>
       <c r="E21" t="str">
         <v>-</v>
@@ -2638,13 +2638,13 @@
         <v>08/19/2025</v>
       </c>
       <c r="B22" t="str">
-        <v>$992.76</v>
+        <v>$8,421.72</v>
       </c>
       <c r="C22" t="str">
         <v>275 ZBA Credit</v>
       </c>
       <c r="D22" t="str">
-        <v>FUND FROM DDA</v>
+        <v>SWEEP FROM DDA</v>
       </c>
       <c r="E22" t="str">
         <v>-</v>
@@ -2672,13 +2672,13 @@
         <v>08/20/2025</v>
       </c>
       <c r="B24" t="str">
-        <v>$1,032.75</v>
+        <v>$574.17</v>
       </c>
       <c r="C24" t="str">
         <v>275 ZBA Credit</v>
       </c>
       <c r="D24" t="str">
-        <v>SWEEP FROM DDA</v>
+        <v>FUND FROM DDA</v>
       </c>
       <c r="E24" t="str">
         <v>-</v>
@@ -2689,7 +2689,7 @@
         <v>08/20/2025</v>
       </c>
       <c r="B25" t="str">
-        <v>$2,655.91</v>
+        <v>$1,032.75</v>
       </c>
       <c r="C25" t="str">
         <v>275 ZBA Credit</v>
@@ -2706,13 +2706,13 @@
         <v>08/20/2025</v>
       </c>
       <c r="B26" t="str">
-        <v>$574.17</v>
+        <v>$2,655.91</v>
       </c>
       <c r="C26" t="str">
         <v>275 ZBA Credit</v>
       </c>
       <c r="D26" t="str">
-        <v>FUND FROM DDA</v>
+        <v>SWEEP FROM DDA</v>
       </c>
       <c r="E26" t="str">
         <v>-</v>
@@ -2757,7 +2757,7 @@
         <v>08/22/2025</v>
       </c>
       <c r="B29" t="str">
-        <v>$22,964.00</v>
+        <v>$1,299.81</v>
       </c>
       <c r="C29" t="str">
         <v>275 ZBA Credit</v>
@@ -2774,7 +2774,7 @@
         <v>08/22/2025</v>
       </c>
       <c r="B30" t="str">
-        <v>$2,126.25</v>
+        <v>$1,665.00</v>
       </c>
       <c r="C30" t="str">
         <v>275 ZBA Credit</v>
@@ -2791,7 +2791,7 @@
         <v>08/22/2025</v>
       </c>
       <c r="B31" t="str">
-        <v>$2,700.00</v>
+        <v>$1,710.00</v>
       </c>
       <c r="C31" t="str">
         <v>275 ZBA Credit</v>
@@ -2808,7 +2808,7 @@
         <v>08/22/2025</v>
       </c>
       <c r="B32" t="str">
-        <v>$3,340.52</v>
+        <v>$2,126.25</v>
       </c>
       <c r="C32" t="str">
         <v>275 ZBA Credit</v>
@@ -2825,7 +2825,7 @@
         <v>08/22/2025</v>
       </c>
       <c r="B33" t="str">
-        <v>$1,710.00</v>
+        <v>$2,430.00</v>
       </c>
       <c r="C33" t="str">
         <v>275 ZBA Credit</v>
@@ -2842,7 +2842,7 @@
         <v>08/22/2025</v>
       </c>
       <c r="B34" t="str">
-        <v>$2,430.00</v>
+        <v>$2,700.00</v>
       </c>
       <c r="C34" t="str">
         <v>275 ZBA Credit</v>
@@ -2859,7 +2859,7 @@
         <v>08/22/2025</v>
       </c>
       <c r="B35" t="str">
-        <v>$1,665.00</v>
+        <v>$3,174.31</v>
       </c>
       <c r="C35" t="str">
         <v>275 ZBA Credit</v>
@@ -2876,7 +2876,7 @@
         <v>08/22/2025</v>
       </c>
       <c r="B36" t="str">
-        <v>$3,174.31</v>
+        <v>$3,340.52</v>
       </c>
       <c r="C36" t="str">
         <v>275 ZBA Credit</v>
@@ -2893,7 +2893,7 @@
         <v>08/22/2025</v>
       </c>
       <c r="B37" t="str">
-        <v>$1,299.81</v>
+        <v>$22,964.00</v>
       </c>
       <c r="C37" t="str">
         <v>275 ZBA Credit</v>
@@ -2978,13 +2978,13 @@
         <v>08/28/2025</v>
       </c>
       <c r="B42" t="str">
-        <v>$129,748.14</v>
+        <v>$1,428.85</v>
       </c>
       <c r="C42" t="str">
         <v>275 ZBA Credit</v>
       </c>
       <c r="D42" t="str">
-        <v>SWEEP FROM DDA</v>
+        <v>FUND FROM DDA</v>
       </c>
       <c r="E42" t="str">
         <v>-</v>
@@ -2995,13 +2995,13 @@
         <v>08/28/2025</v>
       </c>
       <c r="B43" t="str">
-        <v>$2,449,000.00</v>
+        <v>$129,748.14</v>
       </c>
       <c r="C43" t="str">
-        <v>195 Incoming Money Transfer</v>
+        <v>275 ZBA Credit</v>
       </c>
       <c r="D43" t="str">
-        <v>INCOMING WIREMAMCC I LLCLOAN ADVANCE</v>
+        <v>SWEEP FROM DDA</v>
       </c>
       <c r="E43" t="str">
         <v>-</v>
@@ -3012,13 +3012,13 @@
         <v>08/28/2025</v>
       </c>
       <c r="B44" t="str">
-        <v>$1,428.85</v>
+        <v>$2,449,000.00</v>
       </c>
       <c r="C44" t="str">
-        <v>275 ZBA Credit</v>
+        <v>195 Incoming Money Transfer</v>
       </c>
       <c r="D44" t="str">
-        <v>FUND FROM DDA</v>
+        <v>INCOMING WIREMAMCC I LLCLOAN ADVANCE</v>
       </c>
       <c r="E44" t="str">
         <v>-</v>
@@ -3029,13 +3029,13 @@
         <v>08/29/2025</v>
       </c>
       <c r="B45" t="str">
-        <v>$500,000.00</v>
+        <v>$138,923.32</v>
       </c>
       <c r="C45" t="str">
-        <v>195 Incoming Money Transfer</v>
+        <v>275 ZBA Credit</v>
       </c>
       <c r="D45" t="str">
-        <v>INCOMING WIREPPG FUND II LLCNOTPROVIDED</v>
+        <v>FUND FROM DDA</v>
       </c>
       <c r="E45" t="str">
         <v>-</v>
@@ -3046,13 +3046,13 @@
         <v>08/29/2025</v>
       </c>
       <c r="B46" t="str">
-        <v>$138,923.32</v>
+        <v>$500,000.00</v>
       </c>
       <c r="C46" t="str">
-        <v>275 ZBA Credit</v>
+        <v>195 Incoming Money Transfer</v>
       </c>
       <c r="D46" t="str">
-        <v>FUND FROM DDA</v>
+        <v>INCOMING WIREPPG FUND II LLCNOTPROVIDED</v>
       </c>
       <c r="E46" t="str">
         <v>-</v>
